--- a/data/trans_orig/Q31A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q31A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media en que comenzó a tomar bebidas alcohólicas de forma regular</t>
+          <t>Edad media en que comenzó a tomar bebidas alcohólicas de forma regular (tasa de respuesta: 98,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,39</t>
+          <t>16,96; 17,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 18,17</t>
+          <t>17,22; 18,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 17,26</t>
+          <t>16,58; 17,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,39; 16,99</t>
+          <t>16,44; 17,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,61; 19,9</t>
+          <t>18,66; 19,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,84; 21,98</t>
+          <t>19,9; 21,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,31; 23,83</t>
+          <t>20,25; 24,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 20,89</t>
+          <t>18,44; 20,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,46; 17,96</t>
+          <t>17,47; 17,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 19,01</t>
+          <t>18,16; 19,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,69; 18,82</t>
+          <t>17,75; 18,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 17,66</t>
+          <t>16,98; 17,66</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,07</t>
+          <t>16,84; 17,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,01; 17,29</t>
+          <t>17,02; 17,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,08</t>
+          <t>16,82; 17,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,42 +876,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 18,19</t>
+          <t>17,69; 18,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,55</t>
+          <t>17,92; 18,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 18,44</t>
+          <t>17,84; 18,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 18,72</t>
+          <t>16,73; 18,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,16; 17,41</t>
+          <t>17,16; 17,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 17,66</t>
+          <t>17,35; 17,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,25; 17,52</t>
+          <t>17,24; 17,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,62</t>
+          <t>16,96; 17,64</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,22; 17,65</t>
+          <t>17,24; 17,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 18,03</t>
+          <t>17,44; 18,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,08; 17,67</t>
+          <t>17,1; 17,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,26; 18,07</t>
+          <t>17,26; 18,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,27</t>
+          <t>17,66; 18,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,77</t>
+          <t>17,87; 18,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,89; 18,95</t>
+          <t>17,88; 18,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,81; 18,86</t>
+          <t>17,8; 18,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,44; 17,79</t>
+          <t>17,44; 17,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,71; 18,18</t>
+          <t>17,72; 18,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 18,11</t>
+          <t>17,51; 18,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,55; 18,16</t>
+          <t>17,54; 18,12</t>
         </is>
       </c>
     </row>
@@ -1136,52 +1136,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,0; 17,18</t>
+          <t>17,01; 17,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,22; 17,5</t>
+          <t>17,22; 17,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,89; 17,14</t>
+          <t>16,89; 17,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,27</t>
+          <t>16,99; 17,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 18,37</t>
+          <t>17,95; 18,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 19,1</t>
+          <t>18,5; 19,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 18,97</t>
+          <t>18,31; 18,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,09; 18,63</t>
+          <t>17,05; 18,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,34; 17,53</t>
+          <t>17,35; 17,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 17,99</t>
+          <t>17,69; 17,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 17,66</t>
+          <t>17,06; 17,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q31A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q31A-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,69</t>
+          <t>16,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,51</t>
+          <t>19,42</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,27</t>
+          <t>17,25</t>
         </is>
       </c>
     </row>
@@ -716,22 +716,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 17,41</t>
+          <t>16,95; 17,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 18,18</t>
+          <t>17,21; 18,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,58; 17,23</t>
+          <t>16,6; 17,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 17,04</t>
+          <t>16,37; 16,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,37 +741,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,9; 21,83</t>
+          <t>19,92; 22,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,25; 24,09</t>
+          <t>20,23; 23,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,44; 20,92</t>
+          <t>18,46; 20,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,47; 17,96</t>
+          <t>17,46; 17,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 19,08</t>
+          <t>18,15; 19,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,75; 18,95</t>
+          <t>17,72; 18,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 17,66</t>
+          <t>16,92; 17,67</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,06</t>
+          <t>17,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,82</t>
+          <t>18,67</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>17,64</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 17,29</t>
+          <t>17,01; 17,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,08</t>
+          <t>16,81; 17,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,9; 17,24</t>
+          <t>16,93; 17,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 18,18</t>
+          <t>17,67; 18,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,32 +886,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,84; 18,41</t>
+          <t>17,85; 18,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 18,71</t>
+          <t>18,34; 19,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,16; 17,4</t>
+          <t>17,17; 17,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,35; 17,64</t>
+          <t>17,37; 17,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 17,53</t>
+          <t>17,25; 17,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,96; 17,64</t>
+          <t>17,46; 17,81</t>
         </is>
       </c>
     </row>
@@ -943,34 +943,34 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>17,67</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,9</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,27</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,3</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>18,23</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>17,6</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,9</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,27</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,3</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,17</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17,6</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>17,93</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,84</t>
+          <t>17,91</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,24; 17,68</t>
+          <t>17,24; 17,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,44; 18,02</t>
+          <t>17,44; 18,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,67</t>
+          <t>17,1; 17,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,26; 18,01</t>
+          <t>17,34; 18,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,23</t>
+          <t>17,65; 18,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,87; 18,72</t>
+          <t>17,86; 18,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 18,97</t>
+          <t>17,89; 18,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,8; 18,64</t>
+          <t>17,87; 18,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,44; 17,78</t>
+          <t>17,44; 17,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 18,2</t>
+          <t>17,7; 18,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 18,13</t>
+          <t>17,5; 18,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,54; 18,12</t>
+          <t>17,66; 18,2</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,12</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,47</t>
+          <t>17,65</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 17,2</t>
+          <t>17,0; 17,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,22; 17,51</t>
+          <t>17,21; 17,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,89; 17,13</t>
+          <t>16,9; 17,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,29</t>
+          <t>17,02; 17,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 18,35</t>
+          <t>17,96; 18,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,16</t>
+          <t>18,48; 19,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 18,94</t>
+          <t>18,3; 18,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 18,61</t>
+          <t>18,32; 18,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,35; 17,54</t>
+          <t>17,34; 17,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 17,73</t>
+          <t>17,45; 17,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,06; 17,66</t>
+          <t>17,53; 17,79</t>
         </is>
       </c>
     </row>
